--- a/data/metadata_raw/industrial_output.xlsx
+++ b/data/metadata_raw/industrial_output.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1261" uniqueCount="1241">
   <si>
     <t>Code</t>
   </si>
@@ -2852,6 +2852,9 @@
     <t>Бухоро тумани</t>
   </si>
   <si>
+    <t>Вобкент тумани</t>
+  </si>
+  <si>
     <t>Ғиждувон тумани</t>
   </si>
   <si>
@@ -3602,7 +3605,7 @@
     <t>2022-06-29</t>
   </si>
   <si>
-    <t>2024-08-28</t>
+    <t>2025-06-18</t>
   </si>
   <si>
     <t>1.02.01.0001</t>
@@ -6726,7 +6729,7 @@
         <v>724</v>
       </c>
       <c r="E43" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F43">
         <v>18.4</v>
@@ -6788,7 +6791,7 @@
         <v>725</v>
       </c>
       <c r="E44" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="F44">
         <v>98.5</v>
@@ -6850,7 +6853,7 @@
         <v>726</v>
       </c>
       <c r="E45" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="F45">
         <v>20.2</v>
@@ -6912,7 +6915,7 @@
         <v>727</v>
       </c>
       <c r="E46" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="F46">
         <v>58.1</v>
@@ -6974,7 +6977,7 @@
         <v>728</v>
       </c>
       <c r="E47" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="F47">
         <v>680.5</v>
@@ -7036,7 +7039,7 @@
         <v>729</v>
       </c>
       <c r="E48" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="F48">
         <v>38.8</v>
@@ -7098,7 +7101,7 @@
         <v>730</v>
       </c>
       <c r="E49" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="F49">
         <v>120.2</v>
@@ -7160,7 +7163,7 @@
         <v>731</v>
       </c>
       <c r="E50" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="F50">
         <v>59.5</v>
@@ -7222,7 +7225,7 @@
         <v>732</v>
       </c>
       <c r="E51" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="F51">
         <v>39.7</v>
@@ -7284,7 +7287,7 @@
         <v>733</v>
       </c>
       <c r="E52" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="F52">
         <v>522.7</v>
@@ -7346,7 +7349,7 @@
         <v>734</v>
       </c>
       <c r="E53" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="F53">
         <v>206.2</v>
@@ -7408,7 +7411,7 @@
         <v>735</v>
       </c>
       <c r="E54" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="F54">
         <v>18.6</v>
@@ -7470,7 +7473,7 @@
         <v>736</v>
       </c>
       <c r="E55" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F55">
         <v>16.5</v>
@@ -7532,7 +7535,7 @@
         <v>737</v>
       </c>
       <c r="E56" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="F56">
         <v>18.4</v>
@@ -7594,7 +7597,7 @@
         <v>738</v>
       </c>
       <c r="E57" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="F57">
         <v>22.4</v>
@@ -7656,7 +7659,7 @@
         <v>739</v>
       </c>
       <c r="E58" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="F58">
         <v>95.40000000000001</v>
@@ -7718,7 +7721,7 @@
         <v>740</v>
       </c>
       <c r="E59" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F59">
         <v>33.2</v>
@@ -7780,7 +7783,7 @@
         <v>741</v>
       </c>
       <c r="E60" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="F60">
         <v>22.7</v>
@@ -7842,7 +7845,7 @@
         <v>742</v>
       </c>
       <c r="E61" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="F61">
         <v>5</v>
@@ -7904,7 +7907,7 @@
         <v>743</v>
       </c>
       <c r="E62" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="F62">
         <v>21</v>
@@ -7966,7 +7969,7 @@
         <v>744</v>
       </c>
       <c r="E63" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="F63">
         <v>47.7</v>
@@ -8028,7 +8031,7 @@
         <v>745</v>
       </c>
       <c r="E64" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F64">
         <v>13.2</v>
@@ -8090,7 +8093,7 @@
         <v>746</v>
       </c>
       <c r="E65" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="F65">
         <v>2.4</v>
@@ -8152,7 +8155,7 @@
         <v>747</v>
       </c>
       <c r="E66" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="F66">
         <v>4957.5</v>
@@ -8214,7 +8217,7 @@
         <v>748</v>
       </c>
       <c r="E67" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="F67">
         <v>715.4</v>
@@ -8276,7 +8279,7 @@
         <v>749</v>
       </c>
       <c r="E68" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -8338,7 +8341,7 @@
         <v>750</v>
       </c>
       <c r="E69" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -8400,7 +8403,7 @@
         <v>751</v>
       </c>
       <c r="E70" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="F70">
         <v>1110.8</v>
@@ -8462,7 +8465,7 @@
         <v>752</v>
       </c>
       <c r="E71" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="F71">
         <v>27.5</v>
@@ -8524,7 +8527,7 @@
         <v>753</v>
       </c>
       <c r="E72" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="F72">
         <v>52.9</v>
@@ -8586,7 +8589,7 @@
         <v>754</v>
       </c>
       <c r="E73" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="F73">
         <v>55.4</v>
@@ -8648,7 +8651,7 @@
         <v>755</v>
       </c>
       <c r="E74" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="F74">
         <v>105.1</v>
@@ -8710,7 +8713,7 @@
         <v>756</v>
       </c>
       <c r="E75" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="F75">
         <v>22.4</v>
@@ -8772,7 +8775,7 @@
         <v>757</v>
       </c>
       <c r="E76" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="F76">
         <v>47.1</v>
@@ -8834,7 +8837,7 @@
         <v>758</v>
       </c>
       <c r="E77" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="F77">
         <v>2536.4</v>
@@ -8896,7 +8899,7 @@
         <v>759</v>
       </c>
       <c r="E78" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F78">
         <v>51.8</v>
@@ -8958,7 +8961,7 @@
         <v>760</v>
       </c>
       <c r="E79" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="F79">
         <v>51</v>
@@ -9020,7 +9023,7 @@
         <v>761</v>
       </c>
       <c r="E80" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="F80">
         <v>30.8</v>
@@ -9082,7 +9085,7 @@
         <v>762</v>
       </c>
       <c r="E81" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F81">
         <v>112.5</v>
@@ -9144,7 +9147,7 @@
         <v>763</v>
       </c>
       <c r="E82" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="F82">
         <v>38.5</v>
@@ -9206,7 +9209,7 @@
         <v>764</v>
       </c>
       <c r="E83" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="F83">
         <v>4038.5</v>
@@ -9268,7 +9271,7 @@
         <v>765</v>
       </c>
       <c r="E84" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="F84">
         <v>3578.4</v>
@@ -9330,7 +9333,7 @@
         <v>766</v>
       </c>
       <c r="E85" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="F85">
         <v>52.7</v>
@@ -9392,7 +9395,7 @@
         <v>767</v>
       </c>
       <c r="E86" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9454,7 +9457,7 @@
         <v>768</v>
       </c>
       <c r="E87" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="F87">
         <v>5</v>
@@ -9516,7 +9519,7 @@
         <v>769</v>
       </c>
       <c r="E88" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F88">
         <v>59.4</v>
@@ -9578,7 +9581,7 @@
         <v>770</v>
       </c>
       <c r="E89" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="F89">
         <v>41.5</v>
@@ -9640,7 +9643,7 @@
         <v>771</v>
       </c>
       <c r="E90" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F90">
         <v>255.3</v>
@@ -9702,7 +9705,7 @@
         <v>772</v>
       </c>
       <c r="E91" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="F91">
         <v>6.1</v>
@@ -9764,7 +9767,7 @@
         <v>773</v>
       </c>
       <c r="E92" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="F92">
         <v>1.5</v>
@@ -9826,7 +9829,7 @@
         <v>774</v>
       </c>
       <c r="E93" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="F93">
         <v>6.7</v>
@@ -9888,7 +9891,7 @@
         <v>775</v>
       </c>
       <c r="E94" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="F94">
         <v>31.9</v>
@@ -9950,7 +9953,7 @@
         <v>776</v>
       </c>
       <c r="E95" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="F95">
         <v>1007</v>
@@ -10012,7 +10015,7 @@
         <v>777</v>
       </c>
       <c r="E96" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="F96">
         <v>368.5</v>
@@ -10074,7 +10077,7 @@
         <v>778</v>
       </c>
       <c r="E97" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="F97">
         <v>43.3</v>
@@ -10136,7 +10139,7 @@
         <v>779</v>
       </c>
       <c r="E98" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="F98">
         <v>43</v>
@@ -10198,7 +10201,7 @@
         <v>780</v>
       </c>
       <c r="E99" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F99">
         <v>70.2</v>
@@ -10260,7 +10263,7 @@
         <v>781</v>
       </c>
       <c r="E100" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F100">
         <v>41.2</v>
@@ -10322,7 +10325,7 @@
         <v>782</v>
       </c>
       <c r="E101" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="F101">
         <v>74.40000000000001</v>
@@ -10384,7 +10387,7 @@
         <v>783</v>
       </c>
       <c r="E102" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="F102">
         <v>62.2</v>
@@ -10446,7 +10449,7 @@
         <v>784</v>
       </c>
       <c r="E103" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="F103">
         <v>65.5</v>
@@ -10508,7 +10511,7 @@
         <v>785</v>
       </c>
       <c r="E104" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="F104">
         <v>133.2</v>
@@ -10570,7 +10573,7 @@
         <v>786</v>
       </c>
       <c r="E105" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="F105">
         <v>26.5</v>
@@ -10632,7 +10635,7 @@
         <v>787</v>
       </c>
       <c r="E106" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="F106">
         <v>50.5</v>
@@ -10694,7 +10697,7 @@
         <v>788</v>
       </c>
       <c r="E107" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="F107">
         <v>28.5</v>
@@ -10756,7 +10759,7 @@
         <v>789</v>
       </c>
       <c r="E108" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="F108">
         <v>2011.2</v>
@@ -10818,7 +10821,7 @@
         <v>790</v>
       </c>
       <c r="E109" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="F109">
         <v>1199.8</v>
@@ -10880,7 +10883,7 @@
         <v>791</v>
       </c>
       <c r="E110" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="F110">
         <v>49.6</v>
@@ -10942,7 +10945,7 @@
         <v>792</v>
       </c>
       <c r="E111" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F111">
         <v>39.1</v>
@@ -11004,7 +11007,7 @@
         <v>793</v>
       </c>
       <c r="E112" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="F112">
         <v>15.6</v>
@@ -11066,7 +11069,7 @@
         <v>794</v>
       </c>
       <c r="E113" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="F113">
         <v>71.40000000000001</v>
@@ -11128,7 +11131,7 @@
         <v>795</v>
       </c>
       <c r="E114" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="F114">
         <v>45.1</v>
@@ -11190,7 +11193,7 @@
         <v>796</v>
       </c>
       <c r="E115" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="F115">
         <v>59.5</v>
@@ -11252,7 +11255,7 @@
         <v>797</v>
       </c>
       <c r="E116" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="F116">
         <v>13.2</v>
@@ -11314,7 +11317,7 @@
         <v>798</v>
       </c>
       <c r="E117" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="F117">
         <v>90.8</v>
@@ -11376,7 +11379,7 @@
         <v>799</v>
       </c>
       <c r="E118" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="F118">
         <v>53.6</v>
@@ -11438,7 +11441,7 @@
         <v>800</v>
       </c>
       <c r="E119" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="F119">
         <v>69.59999999999999</v>
@@ -11500,7 +11503,7 @@
         <v>801</v>
       </c>
       <c r="E120" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="F120">
         <v>47.4</v>
@@ -11562,7 +11565,7 @@
         <v>802</v>
       </c>
       <c r="E121" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="F121">
         <v>95.59999999999999</v>
@@ -11624,7 +11627,7 @@
         <v>803</v>
       </c>
       <c r="E122" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="F122">
         <v>7.5</v>
@@ -11686,7 +11689,7 @@
         <v>804</v>
       </c>
       <c r="E123" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="F123">
         <v>116.3</v>
@@ -11748,7 +11751,7 @@
         <v>805</v>
       </c>
       <c r="E124" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="F124">
         <v>37.2</v>
@@ -11810,7 +11813,7 @@
         <v>806</v>
       </c>
       <c r="E125" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="F125">
         <v>756.4</v>
@@ -11872,7 +11875,7 @@
         <v>807</v>
       </c>
       <c r="E126" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="F126">
         <v>92.5</v>
@@ -11934,7 +11937,7 @@
         <v>808</v>
       </c>
       <c r="E127" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="F127">
         <v>13.3</v>
@@ -11996,7 +11999,7 @@
         <v>809</v>
       </c>
       <c r="E128" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="F128">
         <v>38.8</v>
@@ -12058,7 +12061,7 @@
         <v>810</v>
       </c>
       <c r="E129" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -12120,7 +12123,7 @@
         <v>811</v>
       </c>
       <c r="E130" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="F130">
         <v>18.5</v>
@@ -12182,7 +12185,7 @@
         <v>812</v>
       </c>
       <c r="E131" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="F131">
         <v>45.6</v>
@@ -12244,7 +12247,7 @@
         <v>813</v>
       </c>
       <c r="E132" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="F132">
         <v>95.3</v>
@@ -12306,7 +12309,7 @@
         <v>814</v>
       </c>
       <c r="E133" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="F133">
         <v>132.7</v>
@@ -12368,7 +12371,7 @@
         <v>815</v>
       </c>
       <c r="E134" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="F134">
         <v>44.8</v>
@@ -12430,7 +12433,7 @@
         <v>816</v>
       </c>
       <c r="E135" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="F135">
         <v>41</v>
@@ -12492,7 +12495,7 @@
         <v>817</v>
       </c>
       <c r="E136" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="F136">
         <v>43.1</v>
@@ -12554,7 +12557,7 @@
         <v>818</v>
       </c>
       <c r="E137" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="F137">
         <v>16.4</v>
@@ -12616,7 +12619,7 @@
         <v>819</v>
       </c>
       <c r="E138" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="F138">
         <v>27.1</v>
@@ -12678,7 +12681,7 @@
         <v>820</v>
       </c>
       <c r="E139" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="F139">
         <v>64.8</v>
@@ -12740,7 +12743,7 @@
         <v>821</v>
       </c>
       <c r="E140" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="F140">
         <v>82.7</v>
@@ -12802,7 +12805,7 @@
         <v>822</v>
       </c>
       <c r="E141" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="F141">
         <v>926.8</v>
@@ -12864,7 +12867,7 @@
         <v>823</v>
       </c>
       <c r="E142" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="F142">
         <v>116.9</v>
@@ -12926,7 +12929,7 @@
         <v>824</v>
       </c>
       <c r="E143" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="F143">
         <v>387</v>
@@ -12988,7 +12991,7 @@
         <v>825</v>
       </c>
       <c r="E144" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="F144">
         <v>20.4</v>
@@ -13050,7 +13053,7 @@
         <v>826</v>
       </c>
       <c r="E145" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="F145">
         <v>45.8</v>
@@ -13112,7 +13115,7 @@
         <v>827</v>
       </c>
       <c r="E146" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="F146">
         <v>47</v>
@@ -13174,7 +13177,7 @@
         <v>828</v>
       </c>
       <c r="E147" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="F147">
         <v>65.3</v>
@@ -13236,7 +13239,7 @@
         <v>829</v>
       </c>
       <c r="E148" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="F148">
         <v>43.9</v>
@@ -13298,7 +13301,7 @@
         <v>830</v>
       </c>
       <c r="E149" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="F149">
         <v>37.9</v>
@@ -13360,7 +13363,7 @@
         <v>831</v>
       </c>
       <c r="E150" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="F150">
         <v>12.7</v>
@@ -13422,7 +13425,7 @@
         <v>832</v>
       </c>
       <c r="E151" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="F151">
         <v>126.5</v>
@@ -13484,7 +13487,7 @@
         <v>833</v>
       </c>
       <c r="E152" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="F152">
         <v>23.5</v>
@@ -13546,7 +13549,7 @@
         <v>834</v>
       </c>
       <c r="E153" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F153">
         <v>5471.2</v>
@@ -13608,7 +13611,7 @@
         <v>835</v>
       </c>
       <c r="E154" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -13670,7 +13673,7 @@
         <v>836</v>
       </c>
       <c r="E155" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="F155">
         <v>1403.9</v>
@@ -13732,7 +13735,7 @@
         <v>837</v>
       </c>
       <c r="E156" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="F156">
         <v>420.9</v>
@@ -13794,7 +13797,7 @@
         <v>838</v>
       </c>
       <c r="E157" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="F157">
         <v>715.5</v>
@@ -13856,7 +13859,7 @@
         <v>839</v>
       </c>
       <c r="E158" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F158">
         <v>562.1</v>
@@ -13918,7 +13921,7 @@
         <v>840</v>
       </c>
       <c r="E159" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -13980,7 +13983,7 @@
         <v>841</v>
       </c>
       <c r="E160" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="F160">
         <v>0</v>
@@ -14042,7 +14045,7 @@
         <v>842</v>
       </c>
       <c r="E161" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="F161">
         <v>40.6</v>
@@ -14104,7 +14107,7 @@
         <v>843</v>
       </c>
       <c r="E162" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="F162">
         <v>254.9</v>
@@ -14166,7 +14169,7 @@
         <v>844</v>
       </c>
       <c r="E163" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="F163">
         <v>42.3</v>
@@ -14228,7 +14231,7 @@
         <v>845</v>
       </c>
       <c r="E164" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F164">
         <v>225.3</v>
@@ -14290,7 +14293,7 @@
         <v>846</v>
       </c>
       <c r="E165" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="F165">
         <v>38.2</v>
@@ -14352,7 +14355,7 @@
         <v>847</v>
       </c>
       <c r="E166" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="F166">
         <v>50.4</v>
@@ -14414,7 +14417,7 @@
         <v>848</v>
       </c>
       <c r="E167" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="F167">
         <v>415.6</v>
@@ -14476,7 +14479,7 @@
         <v>849</v>
       </c>
       <c r="E168" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="F168">
         <v>69.2</v>
@@ -14538,7 +14541,7 @@
         <v>850</v>
       </c>
       <c r="E169" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F169">
         <v>560.8</v>
@@ -14600,7 +14603,7 @@
         <v>851</v>
       </c>
       <c r="E170" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="F170">
         <v>40.5</v>
@@ -14662,7 +14665,7 @@
         <v>852</v>
       </c>
       <c r="E171" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F171">
         <v>29.2</v>
@@ -14724,7 +14727,7 @@
         <v>853</v>
       </c>
       <c r="E172" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="F172">
         <v>285.5</v>
@@ -14786,7 +14789,7 @@
         <v>854</v>
       </c>
       <c r="E173" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="F173">
         <v>65.90000000000001</v>
@@ -14848,7 +14851,7 @@
         <v>855</v>
       </c>
       <c r="E174" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="F174">
         <v>250.3</v>
@@ -14910,7 +14913,7 @@
         <v>856</v>
       </c>
       <c r="E175" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="F175">
         <v>0</v>
@@ -14972,7 +14975,7 @@
         <v>857</v>
       </c>
       <c r="E176" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F176">
         <v>3265.5</v>
@@ -15034,7 +15037,7 @@
         <v>858</v>
       </c>
       <c r="E177" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F177">
         <v>1913.8</v>
@@ -15096,7 +15099,7 @@
         <v>859</v>
       </c>
       <c r="E178" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="F178">
         <v>336.9</v>
@@ -15158,7 +15161,7 @@
         <v>860</v>
       </c>
       <c r="E179" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="F179">
         <v>349.1</v>
@@ -15220,7 +15223,7 @@
         <v>861</v>
       </c>
       <c r="E180" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="F180">
         <v>50.1</v>
@@ -15282,7 +15285,7 @@
         <v>862</v>
       </c>
       <c r="E181" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="F181">
         <v>17</v>
@@ -15344,7 +15347,7 @@
         <v>863</v>
       </c>
       <c r="E182" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="F182">
         <v>9.4</v>
@@ -15406,7 +15409,7 @@
         <v>864</v>
       </c>
       <c r="E183" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="F183">
         <v>61</v>
@@ -15468,7 +15471,7 @@
         <v>865</v>
       </c>
       <c r="E184" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="F184">
         <v>47.9</v>
@@ -15530,7 +15533,7 @@
         <v>866</v>
       </c>
       <c r="E185" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="F185">
         <v>11.8</v>
@@ -15592,7 +15595,7 @@
         <v>867</v>
       </c>
       <c r="E186" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="F186">
         <v>36.5</v>
@@ -15654,7 +15657,7 @@
         <v>868</v>
       </c>
       <c r="E187" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="F187">
         <v>66</v>
@@ -15716,7 +15719,7 @@
         <v>869</v>
       </c>
       <c r="E188" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="F188">
         <v>50.5</v>
@@ -15778,7 +15781,7 @@
         <v>870</v>
       </c>
       <c r="E189" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F189">
         <v>4.8</v>
@@ -15840,7 +15843,7 @@
         <v>871</v>
       </c>
       <c r="E190" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="F190">
         <v>200.4</v>
@@ -15902,7 +15905,7 @@
         <v>872</v>
       </c>
       <c r="E191" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="F191">
         <v>54.3</v>
@@ -15964,7 +15967,7 @@
         <v>873</v>
       </c>
       <c r="E192" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="F192">
         <v>18.6</v>
@@ -16026,7 +16029,7 @@
         <v>874</v>
       </c>
       <c r="E193" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="F193">
         <v>19.3</v>
@@ -16088,7 +16091,7 @@
         <v>875</v>
       </c>
       <c r="E194" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="F194">
         <v>10.6</v>
@@ -16150,7 +16153,7 @@
         <v>876</v>
       </c>
       <c r="E195" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="F195">
         <v>7.5</v>
@@ -16212,7 +16215,7 @@
         <v>877</v>
       </c>
       <c r="E196" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="F196">
         <v>628.6</v>
@@ -16274,7 +16277,7 @@
         <v>878</v>
       </c>
       <c r="E197" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="F197">
         <v>256.9</v>
@@ -16336,7 +16339,7 @@
         <v>879</v>
       </c>
       <c r="E198" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="F198">
         <v>0</v>
@@ -16398,7 +16401,7 @@
         <v>880</v>
       </c>
       <c r="E199" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="F199">
         <v>47.4</v>
@@ -16460,7 +16463,7 @@
         <v>881</v>
       </c>
       <c r="E200" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="F200">
         <v>34.2</v>
@@ -16522,7 +16525,7 @@
         <v>882</v>
       </c>
       <c r="E201" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F201">
         <v>26.7</v>
@@ -16584,7 +16587,7 @@
         <v>883</v>
       </c>
       <c r="E202" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="F202">
         <v>33.7</v>
@@ -16646,7 +16649,7 @@
         <v>884</v>
       </c>
       <c r="E203" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="F203">
         <v>63.2</v>
@@ -16708,7 +16711,7 @@
         <v>885</v>
       </c>
       <c r="E204" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="F204">
         <v>0</v>
@@ -16770,7 +16773,7 @@
         <v>886</v>
       </c>
       <c r="E205" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="F205">
         <v>58.3</v>
@@ -16832,7 +16835,7 @@
         <v>887</v>
       </c>
       <c r="E206" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="F206">
         <v>21.7</v>
@@ -16894,7 +16897,7 @@
         <v>888</v>
       </c>
       <c r="E207" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="F207">
         <v>36.2</v>
@@ -16956,7 +16959,7 @@
         <v>889</v>
       </c>
       <c r="E208" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="F208">
         <v>24.8</v>
@@ -17018,7 +17021,7 @@
         <v>890</v>
       </c>
       <c r="E209" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="F209">
         <v>25.2</v>
@@ -17080,7 +17083,7 @@
         <v>891</v>
       </c>
       <c r="E210" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="F210">
         <v>6984.4</v>
@@ -17142,7 +17145,7 @@
         <v>892</v>
       </c>
       <c r="E211" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="F211">
         <v>272.7</v>
@@ -17204,7 +17207,7 @@
         <v>893</v>
       </c>
       <c r="E212" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="F212">
         <v>355.4</v>
@@ -17266,7 +17269,7 @@
         <v>894</v>
       </c>
       <c r="E213" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="F213">
         <v>349.1</v>
@@ -17328,7 +17331,7 @@
         <v>895</v>
       </c>
       <c r="E214" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="F214">
         <v>852.4</v>
@@ -17390,7 +17393,7 @@
         <v>896</v>
       </c>
       <c r="E215" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="F215">
         <v>586.7</v>
@@ -17452,7 +17455,7 @@
         <v>897</v>
       </c>
       <c r="E216" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="F216">
         <v>1479.6</v>
@@ -17514,7 +17517,7 @@
         <v>898</v>
       </c>
       <c r="E217" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="F217">
         <v>406.4</v>
@@ -17576,7 +17579,7 @@
         <v>899</v>
       </c>
       <c r="E218" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="F218">
         <v>515.4</v>
@@ -17638,7 +17641,7 @@
         <v>900</v>
       </c>
       <c r="E219" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="F219">
         <v>366.7</v>
@@ -17700,7 +17703,7 @@
         <v>901</v>
       </c>
       <c r="E220" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="F220">
         <v>756.5</v>
@@ -17762,7 +17765,7 @@
         <v>902</v>
       </c>
       <c r="E221" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="F221">
         <v>0</v>
@@ -17824,7 +17827,7 @@
         <v>903</v>
       </c>
       <c r="E222" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="F222">
         <v>1043.5</v>
@@ -17884,184 +17887,184 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B2" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C2" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D2" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="F2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="G2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H2" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C3" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D3" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="E3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="F3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="G3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H3" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B4" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C4" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="D4" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="E4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="F4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="G4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="H4" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C5" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="E5" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="F5" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="G5" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="H5" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B6" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="C6" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E6" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="F6" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="G6" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="H6" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B7" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C7" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="D7" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="E7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="F7" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="G7" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="H7" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -18069,259 +18072,259 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="C8" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="D8" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E8" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="F8" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="G8" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="H8" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B9" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C9" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="D9" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B10" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C10" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D10" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="E10" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="F10" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="G10" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="H10" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B11" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C11" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D11" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="E11" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="G11" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="H11" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B12" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="C12" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="D12" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="E12" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="F12" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="G12" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H12" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B13" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C13" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="D13" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="E13" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="F13" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="G13" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="H13" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B14" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="C14" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D14" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="E14" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="F14" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="G14" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="H14" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B15" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="C15" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="D15" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="E15" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="F15" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="G15" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="H15" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B16" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C16" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="D16" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="E16" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="F16" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="G16" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="H16" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B17" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C17" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="D17" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="E17" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="F17" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="G17" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H17" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
     </row>
   </sheetData>
